--- a/output/2026年2月党费汇总表.xlsx
+++ b/output/2026年2月党费汇总表.xlsx
@@ -72,7 +72,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -84,12 +84,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -459,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -516,54 +510,37 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>教工第一支部</t>
+          <t>研究生第一党支部</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>20.6</v>
+        <v>0</v>
       </c>
       <c r="E4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>本科生第一支部</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="5" t="n">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="E6" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A5:B5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
